--- a/product_upload/packages/36/file.xlsx
+++ b/product_upload/packages/36/file.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT101"/>
+  <dimension ref="A1:AU101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacture Name</t>
+          <t>Manufacturer Name</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -649,6 +649,11 @@
         </is>
       </c>
       <c r="AT1" t="inlineStr">
+        <is>
+          <t>Name / En</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -673,7 +678,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -844,6 +849,11 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
+          <t>TRUSOPT</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
           <t>SKU-F39C29A7B620</t>
         </is>
       </c>
@@ -867,7 +877,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1030,6 +1040,11 @@
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="inlineStr">
         <is>
+          <t>ALDACTONE TAB</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
           <t>SKU-29269822BD1B</t>
         </is>
       </c>
@@ -1053,7 +1068,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1224,6 +1239,11 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
+          <t>ALDACTONE TAB</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
           <t>SKU-5E252BD492D8</t>
         </is>
       </c>
@@ -1247,7 +1267,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1414,6 +1434,11 @@
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="inlineStr">
         <is>
+          <t>ZERSA 600 mg Film-coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
           <t>SKU-7045A3855C67</t>
         </is>
       </c>
@@ -1437,7 +1462,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1612,6 +1637,11 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
+          <t>SEFARIX 300 mg Capsule</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
           <t>SKU-934F6482E4AF</t>
         </is>
       </c>
@@ -1635,7 +1665,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1810,6 +1840,11 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
+          <t>LEUKERAN 2 MG. TAB.</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
           <t>SKU-B90D150880C1</t>
         </is>
       </c>
@@ -1833,7 +1868,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -2000,6 +2035,11 @@
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="inlineStr">
         <is>
+          <t>DIPROSONE CREAM 0.05%</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
           <t>SKU-9A24370CDCA5</t>
         </is>
       </c>
@@ -2023,7 +2063,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>KOREA</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2192,6 +2232,11 @@
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="inlineStr">
         <is>
+          <t>AMARYL M 2/500 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
           <t>SKU-B525CA218023</t>
         </is>
       </c>
@@ -2215,7 +2260,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Puerto Rico</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2378,6 +2423,11 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
+          <t>SEVOFLURANE Inhalation Anesthetic</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
           <t>SKU-FBB65E94B12F</t>
         </is>
       </c>
@@ -2401,7 +2451,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2568,6 +2618,11 @@
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="inlineStr">
         <is>
+          <t>BISOLOL 2.5 mg Tablet</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
           <t>SKU-4C8B7EC84485</t>
         </is>
       </c>
@@ -2591,7 +2646,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2762,6 +2817,11 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
+          <t>BISOLOL 5 mg Tablet</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
           <t>SKU-CF4A57C26FA2</t>
         </is>
       </c>
@@ -2785,7 +2845,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2944,6 +3004,11 @@
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="inlineStr">
         <is>
+          <t>BISOLOL 10 mg Tablet</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
           <t>SKU-77EE2B289341</t>
         </is>
       </c>
@@ -2967,7 +3032,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -3138,6 +3203,11 @@
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="inlineStr">
         <is>
+          <t>FLUCAZOL 50 mg Capsule</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
           <t>SKU-5721719B7979</t>
         </is>
       </c>
@@ -3161,7 +3231,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -3324,6 +3394,11 @@
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="inlineStr">
         <is>
+          <t>FLUCAZOL 150 mg Capsule</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
           <t>SKU-369D9F1E3779</t>
         </is>
       </c>
@@ -3347,7 +3422,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -3518,6 +3593,11 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
+          <t>MONCAS 10 mg Film Coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
           <t>SKU-43E511706D36</t>
         </is>
       </c>
@@ -3541,7 +3621,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -3708,6 +3788,11 @@
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="inlineStr">
         <is>
+          <t>MONCAS 4 mg Chewable Tablet</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
           <t>SKU-260AFAF62FF6</t>
         </is>
       </c>
@@ -3731,7 +3816,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -3902,6 +3987,11 @@
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="inlineStr">
         <is>
+          <t>OFEV 150 mg Soft Capsule</t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
           <t>SKU-7D31792F2F16</t>
         </is>
       </c>
@@ -3925,7 +4015,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -4092,6 +4182,11 @@
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="inlineStr">
         <is>
+          <t>RUMAFEN 1% gel</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
           <t>SKU-36F3DA6F241A</t>
         </is>
       </c>
@@ -4115,7 +4210,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -4278,6 +4373,11 @@
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="inlineStr">
         <is>
+          <t>ZEGA 75 MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
           <t>SKU-E198DD2589DD</t>
         </is>
       </c>
@@ -4301,7 +4401,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -4468,6 +4568,11 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
+          <t>ZEGA 150 MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
           <t>SKU-18F0FFC21BC0</t>
         </is>
       </c>
@@ -4491,7 +4596,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -4658,6 +4763,11 @@
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="inlineStr">
         <is>
+          <t>DESLIN 2.5mg/5ml Oral Solution</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
           <t>SKU-183348D49A44</t>
         </is>
       </c>
@@ -4681,7 +4791,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -4844,6 +4954,11 @@
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="inlineStr">
         <is>
+          <t>TULIP 10 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
           <t>SKU-318DBD1AECB7</t>
         </is>
       </c>
@@ -4867,7 +4982,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -5030,6 +5145,11 @@
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="inlineStr">
         <is>
+          <t>TULIP 20 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
           <t>SKU-DB133F8CDEA2</t>
         </is>
       </c>
@@ -5053,7 +5173,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -5216,6 +5336,11 @@
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="inlineStr">
         <is>
+          <t>TULIP 40 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
           <t>SKU-9F992E5D212E</t>
         </is>
       </c>
@@ -5239,7 +5364,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -5414,6 +5539,11 @@
       </c>
       <c r="AT26" t="inlineStr">
         <is>
+          <t>TULIP 80 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
           <t>SKU-B442BCCC713C</t>
         </is>
       </c>
@@ -5437,7 +5567,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -5604,6 +5734,11 @@
       </c>
       <c r="AT27" t="inlineStr">
         <is>
+          <t>AMLOHOPE 10 mg/10 mg Capsule</t>
+        </is>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
           <t>SKU-FEAC556D20FA</t>
         </is>
       </c>
@@ -5627,7 +5762,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -5794,6 +5929,11 @@
       </c>
       <c r="AT28" t="inlineStr">
         <is>
+          <t>AMLOHOPE 10 mg/5 mg Capsule</t>
+        </is>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
           <t>SKU-212BB0F33DE2</t>
         </is>
       </c>
@@ -5817,7 +5957,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -5980,6 +6120,11 @@
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="inlineStr">
         <is>
+          <t>AMLOHOPE 5 mg/10 mg Capsule</t>
+        </is>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
           <t>SKU-9377620FA10A</t>
         </is>
       </c>
@@ -6003,7 +6148,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -6170,6 +6315,11 @@
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="inlineStr">
         <is>
+          <t>SEVIKAR HCT 20/5/12.5MG FILM COATED  TABLET</t>
+        </is>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
           <t>SKU-31891D7A6EA4</t>
         </is>
       </c>
@@ -6193,7 +6343,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -6360,6 +6510,11 @@
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="inlineStr">
         <is>
+          <t>SEVIKAR HCT 40/5/12.5MG FILM COATED  TABLET</t>
+        </is>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
           <t>SKU-9B9A504BCA8B</t>
         </is>
       </c>
@@ -6383,7 +6538,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -6550,6 +6705,11 @@
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="inlineStr">
         <is>
+          <t>SEVIKAR HCT 40/5/25MG FILM COATED  TABLET</t>
+        </is>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
           <t>SKU-B5FAF5C10C32</t>
         </is>
       </c>
@@ -6573,7 +6733,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -6744,6 +6904,11 @@
       </c>
       <c r="AT33" t="inlineStr">
         <is>
+          <t>SEVIKAR HCT 40/10/12.5MG FILM COATED  TABLET</t>
+        </is>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
           <t>SKU-2A8F32CB6B91</t>
         </is>
       </c>
@@ -6767,7 +6932,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -6934,6 +7099,11 @@
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="inlineStr">
         <is>
+          <t>SEVIKAR HCT 40/10/25MG FILM COATED  TABLET</t>
+        </is>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
           <t>SKU-ABFCF3513033</t>
         </is>
       </c>
@@ -6957,7 +7127,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -7120,6 +7290,11 @@
       </c>
       <c r="AT35" t="inlineStr">
         <is>
+          <t>RESOCAL 99.934% POWDER FOR USE IN DRINKING WATER</t>
+        </is>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
           <t>SKU-799F0C2F6A3B</t>
         </is>
       </c>
@@ -7143,7 +7318,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -7310,6 +7485,11 @@
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="inlineStr">
         <is>
+          <t>RESOCAL 99.934% POWDER FOR USE IN DRINKING WATER</t>
+        </is>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
           <t>SKU-5C87F7D719B8</t>
         </is>
       </c>
@@ -7333,7 +7513,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -7506,6 +7686,11 @@
       </c>
       <c r="AT37" t="inlineStr">
         <is>
+          <t>ROXONIN TAPE 50 mg Cutaneous Patch</t>
+        </is>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
           <t>SKU-C4405195D28E</t>
         </is>
       </c>
@@ -7529,7 +7714,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -7696,6 +7881,11 @@
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="inlineStr">
         <is>
+          <t>RINA 0.5 mg/ml Syrup</t>
+        </is>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
           <t>SKU-5A653E30AC5E</t>
         </is>
       </c>
@@ -7719,7 +7909,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -7890,6 +8080,11 @@
       </c>
       <c r="AT39" t="inlineStr">
         <is>
+          <t>CANESTEN-1 VAG.TAB 500MG WITH APPLICATOR</t>
+        </is>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
           <t>SKU-4B7C0E6913C5</t>
         </is>
       </c>
@@ -7913,7 +8108,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -8086,6 +8281,11 @@
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="inlineStr">
         <is>
+          <t>ZYLORIC 100MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
           <t>SKU-D84D5564F3F2</t>
         </is>
       </c>
@@ -8109,7 +8309,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -8264,6 +8464,11 @@
       <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="inlineStr">
         <is>
+          <t>DIFICLIR 200 mg Film Coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
           <t>SKU-0102BE42BE89</t>
         </is>
       </c>
@@ -8287,7 +8492,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -8456,6 +8661,11 @@
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="inlineStr">
         <is>
+          <t>ROXONIN TAPE 100 mg Cutaneous Patch</t>
+        </is>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
           <t>SKU-5475198C0DB0</t>
         </is>
       </c>
@@ -8479,7 +8689,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -8652,6 +8862,11 @@
       </c>
       <c r="AT43" t="inlineStr">
         <is>
+          <t>APROVEL 300MG TAB</t>
+        </is>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
           <t>SKU-7B2F9F27B3FA</t>
         </is>
       </c>
@@ -8675,7 +8890,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -8844,6 +9059,11 @@
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="inlineStr">
         <is>
+          <t>APROVEL 150MG TAB</t>
+        </is>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
           <t>SKU-03C9C6AF7186</t>
         </is>
       </c>
@@ -8867,7 +9087,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -9034,6 +9254,11 @@
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="inlineStr">
         <is>
+          <t>ROLENIUM 500/50 mcg Elpenhaler</t>
+        </is>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
           <t>SKU-B4A025457750</t>
         </is>
       </c>
@@ -9057,7 +9282,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -9220,6 +9445,11 @@
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="inlineStr">
         <is>
+          <t>ALADIN 50 mg film-coated tablets</t>
+        </is>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
           <t>SKU-1A37498C87ED</t>
         </is>
       </c>
@@ -9243,7 +9473,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -9420,6 +9650,11 @@
       </c>
       <c r="AT47" t="inlineStr">
         <is>
+          <t>MIDIXIME 400 mg Capsules</t>
+        </is>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
           <t>SKU-CFA800051007</t>
         </is>
       </c>
@@ -9443,7 +9678,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -9608,6 +9843,11 @@
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="inlineStr">
         <is>
+          <t>MIDIXIME 200 mg Capsules</t>
+        </is>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
           <t>SKU-0AA4DCAA52EA</t>
         </is>
       </c>
@@ -9631,7 +9871,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -9800,6 +10040,11 @@
       <c r="AS49" t="inlineStr"/>
       <c r="AT49" t="inlineStr">
         <is>
+          <t>DESLIN 5 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
           <t>SKU-FAAA58459A07</t>
         </is>
       </c>
@@ -9823,7 +10068,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -9994,6 +10239,11 @@
       </c>
       <c r="AT50" t="inlineStr">
         <is>
+          <t>NUROFEN FOR CHILDREN STRAWBERRY ORAL SUSPENSION</t>
+        </is>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
           <t>SKU-A5699B5309F9</t>
         </is>
       </c>
@@ -10017,7 +10267,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -10184,6 +10434,11 @@
       <c r="AS51" t="inlineStr"/>
       <c r="AT51" t="inlineStr">
         <is>
+          <t>LEVOZAL 0.5 mg/ml Syrup</t>
+        </is>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
           <t>SKU-2B1428157E34</t>
         </is>
       </c>
@@ -10207,7 +10462,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -10370,6 +10625,11 @@
       <c r="AS52" t="inlineStr"/>
       <c r="AT52" t="inlineStr">
         <is>
+          <t>BETAGEN 24 mg tablet</t>
+        </is>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
           <t>SKU-06F301E9409C</t>
         </is>
       </c>
@@ -10393,7 +10653,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -10552,6 +10812,11 @@
       <c r="AS53" t="inlineStr"/>
       <c r="AT53" t="inlineStr">
         <is>
+          <t>ALADIN 25 mg film-coated tablets</t>
+        </is>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
           <t>SKU-B8E57612D2FE</t>
         </is>
       </c>
@@ -10575,7 +10840,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -10750,6 +11015,11 @@
       <c r="AS54" t="inlineStr"/>
       <c r="AT54" t="inlineStr">
         <is>
+          <t>ASPIRIN ADULT TAB 300MG</t>
+        </is>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
           <t>SKU-DD607822AF22</t>
         </is>
       </c>
@@ -10773,7 +11043,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -10928,6 +11198,11 @@
       <c r="AS55" t="inlineStr"/>
       <c r="AT55" t="inlineStr">
         <is>
+          <t>ARVIDA 0.5 mg Tablet</t>
+        </is>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
           <t>SKU-82455484DCCE</t>
         </is>
       </c>
@@ -10951,7 +11226,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -11114,6 +11389,11 @@
       </c>
       <c r="AT56" t="inlineStr">
         <is>
+          <t>QATPEN XR 200 mg tablet</t>
+        </is>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
           <t>SKU-75F4EEA3B1D7</t>
         </is>
       </c>
@@ -11137,7 +11417,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -11296,6 +11576,11 @@
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="inlineStr">
         <is>
+          <t>QATPEN XR 300 mg tablet</t>
+        </is>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
           <t>SKU-69AF193D4887</t>
         </is>
       </c>
@@ -11319,7 +11604,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -11482,6 +11767,11 @@
       </c>
       <c r="AT58" t="inlineStr">
         <is>
+          <t>QATPEN XR 400 mg tablet</t>
+        </is>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
           <t>SKU-F8599F33665E</t>
         </is>
       </c>
@@ -11505,7 +11795,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -11666,6 +11956,11 @@
       <c r="AS59" t="inlineStr"/>
       <c r="AT59" t="inlineStr">
         <is>
+          <t>LEVETAM 500 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
           <t>SKU-0C3DF0BBBB6A</t>
         </is>
       </c>
@@ -11689,7 +11984,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -11856,6 +12151,11 @@
       <c r="AS60" t="inlineStr"/>
       <c r="AT60" t="inlineStr">
         <is>
+          <t>FORMIT XR 750 MG TABLETS</t>
+        </is>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
           <t>SKU-C57EDB67549D</t>
         </is>
       </c>
@@ -11879,7 +12179,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -12046,6 +12346,11 @@
       <c r="AS61" t="inlineStr"/>
       <c r="AT61" t="inlineStr">
         <is>
+          <t>FORMIT XR 750 MG TABLETS</t>
+        </is>
+      </c>
+      <c r="AU61" t="inlineStr">
+        <is>
           <t>SKU-0E23F87C32AF</t>
         </is>
       </c>
@@ -12069,7 +12374,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -12236,6 +12541,11 @@
       <c r="AS62" t="inlineStr"/>
       <c r="AT62" t="inlineStr">
         <is>
+          <t>DEPOJOY 60 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU62" t="inlineStr">
+        <is>
           <t>SKU-6A9F803C1E24</t>
         </is>
       </c>
@@ -12259,7 +12569,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -12422,6 +12732,11 @@
       <c r="AS63" t="inlineStr"/>
       <c r="AT63" t="inlineStr">
         <is>
+          <t>FYCOMPA 4 mg Film-Coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
           <t>SKU-DD032BF3E3EA</t>
         </is>
       </c>
@@ -12445,7 +12760,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -12612,6 +12927,11 @@
       <c r="AS64" t="inlineStr"/>
       <c r="AT64" t="inlineStr">
         <is>
+          <t>FYCOMPA 6 mg Film-Coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU64" t="inlineStr">
+        <is>
           <t>SKU-76C98FD17810</t>
         </is>
       </c>
@@ -12635,7 +12955,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -12798,6 +13118,11 @@
       <c r="AS65" t="inlineStr"/>
       <c r="AT65" t="inlineStr">
         <is>
+          <t>FYCOMPA 8 mg Film-Coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
           <t>SKU-EB01F8C7F6A5</t>
         </is>
       </c>
@@ -12821,7 +13146,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -12980,6 +13305,11 @@
       <c r="AS66" t="inlineStr"/>
       <c r="AT66" t="inlineStr">
         <is>
+          <t>FYCOMPA 10 mg Film-Coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU66" t="inlineStr">
+        <is>
           <t>SKU-0CA4EFFDED73</t>
         </is>
       </c>
@@ -13003,7 +13333,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -13162,6 +13492,11 @@
       <c r="AS67" t="inlineStr"/>
       <c r="AT67" t="inlineStr">
         <is>
+          <t>FYCOMPA 12 mg Film-Coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU67" t="inlineStr">
+        <is>
           <t>SKU-7B1FB771C783</t>
         </is>
       </c>
@@ -13185,7 +13520,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -13364,6 +13699,11 @@
       </c>
       <c r="AT68" t="inlineStr">
         <is>
+          <t>TRULICITY 0.75 mg Solution for Injection in Prefilled Pen</t>
+        </is>
+      </c>
+      <c r="AU68" t="inlineStr">
+        <is>
           <t>SKU-1AA8762E836E</t>
         </is>
       </c>
@@ -13387,7 +13727,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -13558,6 +13898,11 @@
       <c r="AS69" t="inlineStr"/>
       <c r="AT69" t="inlineStr">
         <is>
+          <t>TRULICITY 1.5 mg Solution for Injection in Prefilled Pen</t>
+        </is>
+      </c>
+      <c r="AU69" t="inlineStr">
+        <is>
           <t>SKU-A07B1286FBAF</t>
         </is>
       </c>
@@ -13581,7 +13926,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -13744,6 +14089,11 @@
       <c r="AS70" t="inlineStr"/>
       <c r="AT70" t="inlineStr">
         <is>
+          <t>TOUJEO 300 IU/ml Solution for Injection in Pre-filled Pen</t>
+        </is>
+      </c>
+      <c r="AU70" t="inlineStr">
+        <is>
           <t>SKU-A789FB12A9EA</t>
         </is>
       </c>
@@ -13767,7 +14117,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -13940,6 +14290,11 @@
       <c r="AS71" t="inlineStr"/>
       <c r="AT71" t="inlineStr">
         <is>
+          <t>TOUJEO 300 IU/ml Solution for Injection in Pre-filled Pen</t>
+        </is>
+      </c>
+      <c r="AU71" t="inlineStr">
+        <is>
           <t>SKU-9467F2E7B65A</t>
         </is>
       </c>
@@ -13963,7 +14318,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -14126,6 +14481,11 @@
       <c r="AS72" t="inlineStr"/>
       <c r="AT72" t="inlineStr">
         <is>
+          <t>DEPOJOY 30 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU72" t="inlineStr">
+        <is>
           <t>SKU-04FEB9572861</t>
         </is>
       </c>
@@ -14149,7 +14509,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -14316,6 +14676,11 @@
       </c>
       <c r="AT73" t="inlineStr">
         <is>
+          <t>ANTIKAST 4 mg chewable tablet</t>
+        </is>
+      </c>
+      <c r="AU73" t="inlineStr">
+        <is>
           <t>SKU-F7072B2692A4</t>
         </is>
       </c>
@@ -14339,7 +14704,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -14502,6 +14867,11 @@
       <c r="AS74" t="inlineStr"/>
       <c r="AT74" t="inlineStr">
         <is>
+          <t>ANTIKAST 5 mg chewable tablet</t>
+        </is>
+      </c>
+      <c r="AU74" t="inlineStr">
+        <is>
           <t>SKU-6A19F2077825</t>
         </is>
       </c>
@@ -14525,7 +14895,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -14696,6 +15066,11 @@
       </c>
       <c r="AT75" t="inlineStr">
         <is>
+          <t>TENORYL PLUS 5 mg/5 mg TABLET</t>
+        </is>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
           <t>SKU-E0830E21B52C</t>
         </is>
       </c>
@@ -14719,7 +15094,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -14886,6 +15261,11 @@
       <c r="AS76" t="inlineStr"/>
       <c r="AT76" t="inlineStr">
         <is>
+          <t>TENORYL PLUS 5 mg/10 mg TABLET</t>
+        </is>
+      </c>
+      <c r="AU76" t="inlineStr">
+        <is>
           <t>SKU-2CA4DE90F7C1</t>
         </is>
       </c>
@@ -14909,7 +15289,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -15076,6 +15456,11 @@
       <c r="AS77" t="inlineStr"/>
       <c r="AT77" t="inlineStr">
         <is>
+          <t>TENORYL PLUS 10 mg/5 mg TABLET</t>
+        </is>
+      </c>
+      <c r="AU77" t="inlineStr">
+        <is>
           <t>SKU-DD69638D3127</t>
         </is>
       </c>
@@ -15099,7 +15484,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -15266,6 +15651,11 @@
       <c r="AS78" t="inlineStr"/>
       <c r="AT78" t="inlineStr">
         <is>
+          <t>TENORYL PLUS 10 mg/10 mg TABLET</t>
+        </is>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
           <t>SKU-D655BA554569</t>
         </is>
       </c>
@@ -15289,7 +15679,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -15452,6 +15842,11 @@
       <c r="AS79" t="inlineStr"/>
       <c r="AT79" t="inlineStr">
         <is>
+          <t>MARLON 10 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU79" t="inlineStr">
+        <is>
           <t>SKU-BF1BA1F142BE</t>
         </is>
       </c>
@@ -15475,7 +15870,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -15638,6 +16033,11 @@
       </c>
       <c r="AT80" t="inlineStr">
         <is>
+          <t>MARLON 20 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU80" t="inlineStr">
+        <is>
           <t>SKU-DECF541B17FA</t>
         </is>
       </c>
@@ -15661,7 +16061,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -15832,6 +16232,11 @@
       </c>
       <c r="AT81" t="inlineStr">
         <is>
+          <t>IMODIUM INSTANTS 2MG ORODESPERSIBLE TABLET</t>
+        </is>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
           <t>SKU-21C5617DFA61</t>
         </is>
       </c>
@@ -15855,7 +16260,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -16022,6 +16427,11 @@
       <c r="AS82" t="inlineStr"/>
       <c r="AT82" t="inlineStr">
         <is>
+          <t>IMODIUM INSTANTS 2MG ORODESPERSIBLE TABLET</t>
+        </is>
+      </c>
+      <c r="AU82" t="inlineStr">
+        <is>
           <t>SKU-C93F0ADBDD19</t>
         </is>
       </c>
@@ -16045,7 +16455,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -16216,6 +16626,11 @@
       </c>
       <c r="AT83" t="inlineStr">
         <is>
+          <t>LAVIE 500 mg Film-Coated Tablets</t>
+        </is>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
           <t>SKU-942D38C3BE00</t>
         </is>
       </c>
@@ -16239,7 +16654,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -16402,6 +16817,11 @@
       </c>
       <c r="AT84" t="inlineStr">
         <is>
+          <t>LAVIE 1000 mg Film-Coated Tablets</t>
+        </is>
+      </c>
+      <c r="AU84" t="inlineStr">
+        <is>
           <t>SKU-5818EF604446</t>
         </is>
       </c>
@@ -16425,7 +16845,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -16592,6 +17012,11 @@
       </c>
       <c r="AT85" t="inlineStr">
         <is>
+          <t>ANTIKAST 10 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU85" t="inlineStr">
+        <is>
           <t>SKU-9861D79EE7AD</t>
         </is>
       </c>
@@ -16615,7 +17040,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -16790,6 +17215,11 @@
       </c>
       <c r="AT86" t="inlineStr">
         <is>
+          <t>AMLOHOPE 5 mg/5 mg Capsule</t>
+        </is>
+      </c>
+      <c r="AU86" t="inlineStr">
+        <is>
           <t>SKU-050459AAEF52</t>
         </is>
       </c>
@@ -16813,7 +17243,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -16976,6 +17406,11 @@
       <c r="AS87" t="inlineStr"/>
       <c r="AT87" t="inlineStr">
         <is>
+          <t>LODIPAM 5 mg Film-Coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU87" t="inlineStr">
+        <is>
           <t>SKU-101414EADC7E</t>
         </is>
       </c>
@@ -16999,7 +17434,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -17162,6 +17597,11 @@
       </c>
       <c r="AT88" t="inlineStr">
         <is>
+          <t>CITOXAL 5 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU88" t="inlineStr">
+        <is>
           <t>SKU-D109B115C72B</t>
         </is>
       </c>
@@ -17185,7 +17625,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -17356,6 +17796,11 @@
       </c>
       <c r="AT89" t="inlineStr">
         <is>
+          <t>KEFLEX 250MG-5ML SUSPENTION</t>
+        </is>
+      </c>
+      <c r="AU89" t="inlineStr">
+        <is>
           <t>SKU-F724734B01AA</t>
         </is>
       </c>
@@ -17379,7 +17824,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -17542,6 +17987,11 @@
       <c r="AS90" t="inlineStr"/>
       <c r="AT90" t="inlineStr">
         <is>
+          <t>KEFLEX 500MG TAB</t>
+        </is>
+      </c>
+      <c r="AU90" t="inlineStr">
+        <is>
           <t>SKU-FF68B6E0E6B1</t>
         </is>
       </c>
@@ -17565,7 +18015,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -17732,6 +18182,11 @@
       <c r="AS91" t="inlineStr"/>
       <c r="AT91" t="inlineStr">
         <is>
+          <t>METAZ LOTION 0.1%</t>
+        </is>
+      </c>
+      <c r="AU91" t="inlineStr">
+        <is>
           <t>SKU-94E49A39AA06</t>
         </is>
       </c>
@@ -17755,7 +18210,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -17914,6 +18369,11 @@
       <c r="AS92" t="inlineStr"/>
       <c r="AT92" t="inlineStr">
         <is>
+          <t>METAZ 0.1% W-W OINTMENT</t>
+        </is>
+      </c>
+      <c r="AU92" t="inlineStr">
+        <is>
           <t>SKU-716EBDA8A608</t>
         </is>
       </c>
@@ -17937,7 +18397,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -18108,6 +18568,11 @@
       </c>
       <c r="AT93" t="inlineStr">
         <is>
+          <t>METAZ 0.1% W-W OINTMENT</t>
+        </is>
+      </c>
+      <c r="AU93" t="inlineStr">
+        <is>
           <t>SKU-9DB6310EC17B</t>
         </is>
       </c>
@@ -18131,7 +18596,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -18298,6 +18763,11 @@
       <c r="AS94" t="inlineStr"/>
       <c r="AT94" t="inlineStr">
         <is>
+          <t>METAZ CREAM 0.1%</t>
+        </is>
+      </c>
+      <c r="AU94" t="inlineStr">
+        <is>
           <t>SKU-E20A142DB489</t>
         </is>
       </c>
@@ -18321,7 +18791,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -18492,6 +18962,11 @@
       </c>
       <c r="AT95" t="inlineStr">
         <is>
+          <t>TRACON 100MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="AU95" t="inlineStr">
+        <is>
           <t>SKU-867EACBDC68F</t>
         </is>
       </c>
@@ -18515,7 +18990,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -18686,6 +19161,11 @@
       </c>
       <c r="AT96" t="inlineStr">
         <is>
+          <t>TRACON 100MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="AU96" t="inlineStr">
+        <is>
           <t>SKU-65EC489A6E70</t>
         </is>
       </c>
@@ -18709,7 +19189,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -18874,6 +19354,11 @@
       <c r="AS97" t="inlineStr"/>
       <c r="AT97" t="inlineStr">
         <is>
+          <t>CELEBREX 100MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU97" t="inlineStr">
+        <is>
           <t>SKU-568CFB4C63B5</t>
         </is>
       </c>
@@ -18897,7 +19382,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -19068,6 +19553,11 @@
       </c>
       <c r="AT98" t="inlineStr">
         <is>
+          <t>CELEBREX 200MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU98" t="inlineStr">
+        <is>
           <t>SKU-6CAAE4BB07CB</t>
         </is>
       </c>
@@ -19091,7 +19581,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -19250,6 +19740,11 @@
       <c r="AS99" t="inlineStr"/>
       <c r="AT99" t="inlineStr">
         <is>
+          <t>CELEBREX 200MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU99" t="inlineStr">
+        <is>
           <t>SKU-59FEA40F5D34</t>
         </is>
       </c>
@@ -19273,7 +19768,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -19444,6 +19939,11 @@
       </c>
       <c r="AT100" t="inlineStr">
         <is>
+          <t>DIPROSONE OINTMENT 0.05%</t>
+        </is>
+      </c>
+      <c r="AU100" t="inlineStr">
+        <is>
           <t>SKU-8703FB4B3389</t>
         </is>
       </c>
@@ -19467,7 +19967,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -19629,6 +20129,11 @@
       </c>
       <c r="AS101" t="inlineStr"/>
       <c r="AT101" t="inlineStr">
+        <is>
+          <t>JAKAVI 20MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU101" t="inlineStr">
         <is>
           <t>SKU-08A514B3FB5F</t>
         </is>
@@ -19645,7 +20150,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB12"/>
+  <dimension ref="A1:AC12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19691,100 +20196,105 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Level 1*</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Level 2*</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Level 3*</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Risk Class *</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Sterility</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Model / Catalogue Number</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Single Use</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Legal Manufacturer</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>UDI-DI</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>GMDN Code / Term</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>SFDA Authorized Representative License No.</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Size</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Power Source</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Warranty</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Storage Conditions / En</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Branch id</t>
         </is>
@@ -19816,7 +20326,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -19831,92 +20341,97 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>SKU-23643</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>427.92</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T2" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U2" t="inlineStr">
+      <c r="U2" t="n">
+        <v>308</v>
+      </c>
+      <c r="V2" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W2" t="n">
+      <c r="X2" t="n">
         <v>100</v>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y2" t="n">
+      <c r="Z2" t="n">
         <v>12</v>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19948,7 +20463,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -19963,92 +20478,97 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>SKU-57385</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>295.69</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Thermometer</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T3" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U3" t="inlineStr">
+      <c r="U3" t="n">
+        <v>309</v>
+      </c>
+      <c r="V3" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W3" t="n">
+      <c r="X3" t="n">
         <v>100</v>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y3" t="n">
+      <c r="Z3" t="n">
         <v>12</v>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20080,7 +20600,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -20095,92 +20615,97 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>SKU-72039</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>364.57</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T4" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U4" t="inlineStr">
+      <c r="U4" t="n">
+        <v>310</v>
+      </c>
+      <c r="V4" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
         <v>100</v>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y4" t="n">
+      <c r="Z4" t="n">
         <v>12</v>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20212,7 +20737,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -20227,92 +20752,97 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>SKU-71383</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>33.87</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T5" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U5" t="inlineStr">
+      <c r="U5" t="n">
+        <v>311</v>
+      </c>
+      <c r="V5" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
         <v>100</v>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y5" t="n">
+      <c r="Z5" t="n">
         <v>12</v>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20344,7 +20874,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -20359,92 +20889,97 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>SKU-18189</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>478.21</v>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Thermometer</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T6" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U6" t="inlineStr">
+      <c r="U6" t="n">
+        <v>312</v>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W6" t="n">
+      <c r="X6" t="n">
         <v>100</v>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y6" t="n">
+      <c r="Z6" t="n">
         <v>12</v>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20476,7 +21011,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -20491,92 +21026,97 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>SKU-37317</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>335.76</v>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T7" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U7" t="inlineStr">
+      <c r="U7" t="n">
+        <v>313</v>
+      </c>
+      <c r="V7" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W7" t="n">
+      <c r="X7" t="n">
         <v>100</v>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y7" t="n">
+      <c r="Z7" t="n">
         <v>12</v>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20608,7 +21148,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -20623,92 +21163,97 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>SKU-62874</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>28.42</v>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T8" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U8" t="inlineStr">
+      <c r="U8" t="n">
+        <v>314</v>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W8" t="n">
+      <c r="X8" t="n">
         <v>100</v>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y8" t="n">
+      <c r="Z8" t="n">
         <v>12</v>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20740,7 +21285,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -20755,92 +21300,97 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>SKU-98106</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>64.97</v>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T9" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U9" t="inlineStr">
+      <c r="U9" t="n">
+        <v>315</v>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W9" t="n">
+      <c r="X9" t="n">
         <v>100</v>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y9" t="n">
+      <c r="Z9" t="n">
         <v>12</v>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20872,7 +21422,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -20887,92 +21437,97 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>SKU-95819</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>20.25</v>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T10" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U10" t="inlineStr">
+      <c r="U10" t="n">
+        <v>316</v>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W10" t="n">
+      <c r="X10" t="n">
         <v>100</v>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y10" t="n">
+      <c r="Z10" t="n">
         <v>12</v>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -21004,7 +21559,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -21019,92 +21574,97 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>SKU-18774</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>252.71</v>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T11" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U11" t="inlineStr">
+      <c r="U11" t="n">
+        <v>317</v>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W11" t="n">
+      <c r="X11" t="n">
         <v>100</v>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y11" t="n">
+      <c r="Z11" t="n">
         <v>12</v>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="AA11" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -21136,7 +21696,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -21151,92 +21711,97 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>SKU-27545</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>458.54</v>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T12" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U12" t="inlineStr">
+      <c r="U12" t="n">
+        <v>318</v>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W12" t="n">
+      <c r="X12" t="n">
         <v>100</v>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y12" t="n">
+      <c r="Z12" t="n">
         <v>12</v>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -21253,7 +21818,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U21"/>
+  <dimension ref="A1:W21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21359,6 +21924,16 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Ingredients</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
@@ -21394,7 +21969,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -21459,6 +22034,16 @@
         </is>
       </c>
       <c r="U2" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
         <is>
           <t>SKU-6DC4C9ABAFCF</t>
         </is>
@@ -21495,7 +22080,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -21560,6 +22145,16 @@
         </is>
       </c>
       <c r="U3" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
         <is>
           <t>SKU-1F1CC1818649</t>
         </is>
@@ -21596,7 +22191,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -21661,6 +22256,16 @@
         </is>
       </c>
       <c r="U4" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
         <is>
           <t>SKU-FA1F0C78AC30</t>
         </is>
@@ -21697,7 +22302,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -21762,6 +22367,16 @@
         </is>
       </c>
       <c r="U5" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>SKU-9F1EA1E46627</t>
         </is>
@@ -21798,7 +22413,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -21863,6 +22478,16 @@
         </is>
       </c>
       <c r="U6" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
         <is>
           <t>SKU-1CA6BC3D7F0D</t>
         </is>
@@ -21899,7 +22524,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -21964,6 +22589,16 @@
         </is>
       </c>
       <c r="U7" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
         <is>
           <t>SKU-2A4B16C54758</t>
         </is>
@@ -22000,7 +22635,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -22065,6 +22700,16 @@
         </is>
       </c>
       <c r="U8" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
         <is>
           <t>SKU-973153799D1A</t>
         </is>
@@ -22101,7 +22746,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -22166,6 +22811,16 @@
         </is>
       </c>
       <c r="U9" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
         <is>
           <t>SKU-9819DC7DE086</t>
         </is>
@@ -22202,7 +22857,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -22267,6 +22922,16 @@
         </is>
       </c>
       <c r="U10" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
         <is>
           <t>SKU-1C53672EEC4F</t>
         </is>
@@ -22303,7 +22968,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -22368,6 +23033,16 @@
         </is>
       </c>
       <c r="U11" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
         <is>
           <t>SKU-C6A27E234D98</t>
         </is>
@@ -22404,7 +23079,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -22469,6 +23144,16 @@
         </is>
       </c>
       <c r="U12" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
         <is>
           <t>SKU-74B9873E2123</t>
         </is>
@@ -22505,7 +23190,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -22570,6 +23255,16 @@
         </is>
       </c>
       <c r="U13" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
         <is>
           <t>SKU-DD92E3C9905A</t>
         </is>
@@ -22606,7 +23301,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -22671,6 +23366,16 @@
         </is>
       </c>
       <c r="U14" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
         <is>
           <t>SKU-6B74C218D89F</t>
         </is>
@@ -22707,7 +23412,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -22772,6 +23477,16 @@
         </is>
       </c>
       <c r="U15" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
         <is>
           <t>SKU-236B201545F7</t>
         </is>
@@ -22808,7 +23523,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -22873,6 +23588,16 @@
         </is>
       </c>
       <c r="U16" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
         <is>
           <t>SKU-905955914D5D</t>
         </is>
@@ -22909,7 +23634,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -22974,6 +23699,16 @@
         </is>
       </c>
       <c r="U17" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
         <is>
           <t>SKU-03E62869DB3C</t>
         </is>
@@ -23010,7 +23745,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -23075,6 +23810,16 @@
         </is>
       </c>
       <c r="U18" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
         <is>
           <t>SKU-CD61BDA31366</t>
         </is>
@@ -23111,7 +23856,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -23176,6 +23921,16 @@
         </is>
       </c>
       <c r="U19" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
         <is>
           <t>SKU-F747C3E0F18E</t>
         </is>
@@ -23212,7 +23967,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -23277,6 +24032,16 @@
         </is>
       </c>
       <c r="U20" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
         <is>
           <t>SKU-FEF109832F17</t>
         </is>
@@ -23313,7 +24078,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -23378,6 +24143,16 @@
         </is>
       </c>
       <c r="U21" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
         <is>
           <t>SKU-22244DBDE953</t>
         </is>

--- a/product_upload/packages/36/file.xlsx
+++ b/product_upload/packages/36/file.xlsx
@@ -2268,8 +2268,16 @@
           <t>6430135363-850-937106809682</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SEVOFLURANE Inhalation Anesthetic</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>SEVOFLURANE Inhalation Anesthetic detailed description.</t>
+        </is>
+      </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
@@ -2853,8 +2861,16 @@
           <t>4191715264-239-012217791114</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BISOLOL 10 mg Tablet</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>BISOLOL 10 mg Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
@@ -3239,8 +3255,16 @@
           <t>5829873279-789-566523869270</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FLUCAZOL 150 mg Capsule</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>FLUCAZOL 150 mg Capsule detailed description.</t>
+        </is>
+      </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
@@ -3430,8 +3454,16 @@
           <t>7974962754-341-365776912754</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ MONCAS 10 mg Film Coated Tablet</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>MONCAS 10 mg Film Coated Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
@@ -3629,8 +3661,16 @@
           <t>4137183872-492-629509806230</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ MONCAS 4 mg Chewable Tablet</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>MONCAS 4 mg Chewable Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
@@ -4218,8 +4258,16 @@
           <t>9249655095-694-134583868028</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ZEGA 75 MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>ZEGA 75 MG CAPSULE detailed description.</t>
+        </is>
+      </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
@@ -4409,8 +4457,16 @@
           <t>4589470824-602-566218621518</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ZEGA 150 MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>ZEGA 150 MG CAPSULE detailed description.</t>
+        </is>
+      </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
@@ -4799,8 +4855,16 @@
           <t>0046345557-742-704065164207</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ TULIP 10 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>TULIP 10 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
@@ -4990,8 +5054,16 @@
           <t>2264991805-316-811481007534</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ TULIP 20 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>TULIP 20 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
@@ -5181,8 +5253,16 @@
           <t>3795529369-748-753005928927</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ TULIP 40 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>TULIP 40 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
@@ -5575,8 +5655,16 @@
           <t>1597918881-869-762426862957</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ AMLOHOPE 10 mg/10 mg Capsule</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>AMLOHOPE 10 mg/10 mg Capsule detailed description.</t>
+        </is>
+      </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
@@ -5770,8 +5858,16 @@
           <t>2874432904-626-789515559382</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ AMLOHOPE 10 mg/5 mg Capsule</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>AMLOHOPE 10 mg/5 mg Capsule detailed description.</t>
+        </is>
+      </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
@@ -5965,8 +6061,16 @@
           <t>9015666931-188-986685303512</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ AMLOHOPE 5 mg/10 mg Capsule</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>AMLOHOPE 5 mg/10 mg Capsule detailed description.</t>
+        </is>
+      </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
@@ -7135,8 +7239,16 @@
           <t>9381714575-872-594165482653</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ RESOCAL 99.934% POWDER FOR USE IN DRINKING WATER</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>RESOCAL 99.934% POWDER FOR USE IN DRINKING WATER detailed description.</t>
+        </is>
+      </c>
       <c r="I35" t="n">
         <v>0</v>
       </c>
@@ -8317,8 +8429,16 @@
           <t>3916704730-683-721844317206</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DIFICLIR 200 mg Film Coated Tablet</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>DIFICLIR 200 mg Film Coated Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I41" t="n">
         <v>0</v>
       </c>
@@ -9290,8 +9410,16 @@
           <t>3739324410-979-213989376987</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ALADIN 50 mg film-coated tablets</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>ALADIN 50 mg film-coated tablets detailed description.</t>
+        </is>
+      </c>
       <c r="I46" t="n">
         <v>0</v>
       </c>
@@ -9686,8 +9814,16 @@
           <t>8547535053-076-996579252985</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ MIDIXIME 200 mg Capsules</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>MIDIXIME 200 mg Capsules detailed description.</t>
+        </is>
+      </c>
       <c r="I48" t="inlineStr">
         <is>
           <t>Med city</t>
@@ -10661,8 +10797,16 @@
           <t>0694925203-156-065342984797</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ALADIN 25 mg film-coated tablets</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>ALADIN 25 mg film-coated tablets detailed description.</t>
+        </is>
+      </c>
       <c r="I53" t="n">
         <v>0</v>
       </c>
@@ -11051,8 +11195,16 @@
           <t>1320720048-896-009071147124</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ARVIDA 0.5 mg Tablet</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>ARVIDA 0.5 mg Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I55" t="n">
         <v>0</v>
       </c>
@@ -11234,8 +11386,16 @@
           <t>0716987588-608-876537149860</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ QATPEN XR 200 mg tablet</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>QATPEN XR 200 mg tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I56" t="n">
         <v>0</v>
       </c>
@@ -11425,8 +11585,16 @@
           <t>1238168146-583-402479697634</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ QATPEN XR 300 mg tablet</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>QATPEN XR 300 mg tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I57" t="n">
         <v>0</v>
       </c>
@@ -11612,8 +11780,16 @@
           <t>0951992365-153-275346201490</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ QATPEN XR 400 mg tablet</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>QATPEN XR 400 mg tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I58" t="n">
         <v>0</v>
       </c>
@@ -11803,8 +11979,16 @@
           <t>6268795237-723-115266215401</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LEVETAM 500 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>LEVETAM 500 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I59" t="inlineStr">
         <is>
           <t>SPIMACO</t>
@@ -13154,8 +13338,16 @@
           <t>7273527115-161-147322370932</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FYCOMPA 10 mg Film-Coated Tablet</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>FYCOMPA 10 mg Film-Coated Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I66" t="n">
         <v>0</v>
       </c>
@@ -13341,8 +13533,16 @@
           <t>0674982172-502-319601358628</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FYCOMPA 12 mg Film-Coated Tablet</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>FYCOMPA 12 mg Film-Coated Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I67" t="n">
         <v>0</v>
       </c>
@@ -13934,8 +14134,16 @@
           <t>3460835729-636-308530807185</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ TOUJEO 300 IU/ml Solution for Injection in Pre-filled Pen</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>TOUJEO 300 IU/ml Solution for Injection in Pre-filled Pen detailed description.</t>
+        </is>
+      </c>
       <c r="I70" t="n">
         <v>0</v>
       </c>
@@ -14517,8 +14725,16 @@
           <t>2319357213-988-230435486306</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ANTIKAST 4 mg chewable tablet</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>ANTIKAST 4 mg chewable tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I73" t="n">
         <v>0</v>
       </c>
@@ -14712,8 +14928,16 @@
           <t>4539843223-505-934744908144</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ANTIKAST 5 mg chewable tablet</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>ANTIKAST 5 mg chewable tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I74" t="n">
         <v>0</v>
       </c>
@@ -15878,8 +16102,16 @@
           <t>5901973746-711-772088666135</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ MARLON 20 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>MARLON 20 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I80" t="n">
         <v>0</v>
       </c>
@@ -16662,8 +16894,16 @@
           <t>7860801017-391-755546465719</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LAVIE 1000 mg Film-Coated Tablets</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>LAVIE 1000 mg Film-Coated Tablets detailed description.</t>
+        </is>
+      </c>
       <c r="I84" t="n">
         <v>0</v>
       </c>
@@ -16853,8 +17093,16 @@
           <t>5864621787-490-248502774046</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ANTIKAST 10 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>ANTIKAST 10 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I85" t="n">
         <v>0</v>
       </c>
@@ -17442,8 +17690,16 @@
           <t>1089791187-020-617662922049</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CITOXAL 5 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>CITOXAL 5 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I88" t="n">
         <v>0</v>
       </c>
@@ -18218,8 +18474,16 @@
           <t>9937446352-190-190343120273</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ METAZ 0.1% W-W OINTMENT</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>METAZ 0.1% W-W OINTMENT detailed description.</t>
+        </is>
+      </c>
       <c r="I92" t="n">
         <v>0</v>
       </c>
@@ -19197,8 +19461,16 @@
           <t>3217955958-605-082040016837</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CELEBREX 100MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>CELEBREX 100MG CAPSULE detailed description.</t>
+        </is>
+      </c>
       <c r="I97" t="inlineStr">
         <is>
           <t>PFIZER SAUDI LIMITED</t>
@@ -19589,8 +19861,16 @@
           <t>6761796881-646-323088915884</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CELEBREX 200MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>CELEBREX 200MG CAPSULE detailed description.</t>
+        </is>
+      </c>
       <c r="I99" t="n">
         <v>0</v>
       </c>

--- a/product_upload/packages/36/file.xlsx
+++ b/product_upload/packages/36/file.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -20476,7 +20476,7 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -22098,7 +22098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W21"/>
+  <dimension ref="A1:X21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22179,40 +22179,45 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>Size unit</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>Manufacturer *</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Period After Opening.1</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Warnings</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Manufacturer Name</t>
-        </is>
-      </c>
       <c r="V1" t="inlineStr">
         <is>
+          <t>Manufacturer</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Ingredients</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -22292,38 +22297,43 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>260.33</v>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>SKU-6DC4C9ABAFCF</t>
         </is>
@@ -22403,38 +22413,43 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>426.31</v>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>SKU-1F1CC1818649</t>
         </is>
@@ -22514,38 +22529,43 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>244.8</v>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>SKU-FA1F0C78AC30</t>
         </is>
@@ -22625,38 +22645,43 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>73.28</v>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>SKU-9F1EA1E46627</t>
         </is>
@@ -22736,38 +22761,43 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>405.2</v>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>SKU-1CA6BC3D7F0D</t>
         </is>
@@ -22847,38 +22877,43 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>364.59</v>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>SKU-2A4B16C54758</t>
         </is>
@@ -22958,38 +22993,43 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>86.16</v>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>SKU-973153799D1A</t>
         </is>
@@ -23069,38 +23109,43 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>469.92</v>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>SKU-9819DC7DE086</t>
         </is>
@@ -23180,38 +23225,43 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>87.72</v>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>SKU-1C53672EEC4F</t>
         </is>
@@ -23291,38 +23341,43 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>172.21</v>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>SKU-C6A27E234D98</t>
         </is>
@@ -23402,38 +23457,43 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>243.55</v>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>SKU-74B9873E2123</t>
         </is>
@@ -23513,38 +23573,43 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>174.03</v>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>SKU-DD92E3C9905A</t>
         </is>
@@ -23624,38 +23689,43 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>289.49</v>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>SKU-6B74C218D89F</t>
         </is>
@@ -23735,38 +23805,43 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>51.37</v>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>SKU-236B201545F7</t>
         </is>
@@ -23846,38 +23921,43 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>281.41</v>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>SKU-905955914D5D</t>
         </is>
@@ -23957,38 +24037,43 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>234.08</v>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>SKU-03E62869DB3C</t>
         </is>
@@ -24068,38 +24153,43 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>297.33</v>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>SKU-CD61BDA31366</t>
         </is>
@@ -24179,38 +24269,43 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>26.58</v>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>SKU-F747C3E0F18E</t>
         </is>
@@ -24290,38 +24385,43 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>478.67</v>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>SKU-FEF109832F17</t>
         </is>
@@ -24401,38 +24501,43 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>215.12</v>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>SKU-22244DBDE953</t>
         </is>
